--- a/tests/workbooks/test_ratehelpers.xlsx
+++ b/tests/workbooks/test_ratehelpers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA258476-C7E2-42A2-883C-AB21421C035D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5662AD-C35D-4875-9CF1-BC68311155F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="12" xr2:uid="{60DEDABF-8191-4F74-809B-551F46E87618}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview Tabs" sheetId="18" r:id="rId1"/>
@@ -614,7 +614,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,6 +660,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -681,10 +691,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -715,8 +726,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Prozent" xfId="1" builtinId="5"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1160,10 +1181,10 @@
         <v>33</v>
       </c>
       <c r="B4" s="12">
-        <v>0.6</v>
+        <v>95.5</v>
       </c>
       <c r="C4" s="12">
-        <v>0.1</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1239,11 +1260,11 @@
       </c>
       <c r="B11" s="12">
         <f>_xll.qlRateHelperQuote(B10)</f>
-        <v>0.6</v>
+        <v>95.5</v>
       </c>
       <c r="C11" s="12">
         <f>_xll.qlRateHelperQuote(C10)</f>
-        <v>0.1</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1360,7 +1381,7 @@
         <v>33</v>
       </c>
       <c r="B4" s="12">
-        <v>0.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1407,7 +1428,7 @@
       </c>
       <c r="B10" s="12">
         <f>_xll.qlRateHelperQuote(B9)</f>
-        <v>0.2</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1492,11 +1513,11 @@
       <c r="A4" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="12">
-        <v>0.4</v>
+      <c r="B4" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.04</v>
       </c>
       <c r="D4" s="12"/>
     </row>
@@ -1654,11 +1675,11 @@
       </c>
       <c r="B17" s="12">
         <f>_xll.qlRateHelperQuote(B16)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C17" s="12">
         <f>_xll.qlRateHelperQuote(C16)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1764,10 +1785,10 @@
         <v>93</v>
       </c>
       <c r="B4" s="12">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="C4" s="12">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1926,11 +1947,11 @@
       </c>
       <c r="B18" s="12">
         <f>_xll.qlRateHelperQuote(B17)</f>
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="C18" s="12">
         <f>_xll.qlRateHelperQuote(C17)</f>
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2036,10 +2057,10 @@
         <v>93</v>
       </c>
       <c r="B4" s="12">
-        <v>0.8</v>
+        <v>1E-3</v>
       </c>
       <c r="C4" s="12">
-        <v>0.8</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2209,11 +2230,11 @@
       </c>
       <c r="B19" s="12">
         <f>_xll.qlRateHelperQuote(B18)</f>
-        <v>0.8</v>
+        <v>1E-3</v>
       </c>
       <c r="C19" s="12">
         <f>_xll.qlRateHelperQuote(C18)</f>
-        <v>0.8</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2318,7 +2339,7 @@
         <v>93</v>
       </c>
       <c r="B4" s="12">
-        <v>0.7</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2412,7 +2433,7 @@
       </c>
       <c r="B15" s="12">
         <f>_xll.qlRateHelperQuote(B14)</f>
-        <v>0.7</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2506,7 +2527,7 @@
         <v>93</v>
       </c>
       <c r="B4" s="12">
-        <v>0.3</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2592,7 +2613,7 @@
       </c>
       <c r="B14" s="12">
         <f>_xll.qlRateHelperQuote(B13)</f>
-        <v>0.3</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2924,8 +2945,8 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="12">
-        <v>0.2</v>
+      <c r="B20" s="18">
+        <v>0.02</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -2953,7 +2974,7 @@
       </c>
       <c r="B23" s="12">
         <f>_xll.qlRateHelperQuote(B22)</f>
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3011,8 +3032,8 @@
       <c r="A31" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="12">
-        <v>0.2</v>
+      <c r="B31" s="18">
+        <v>0.02</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3047,7 +3068,7 @@
       </c>
       <c r="B35" s="12">
         <f>_xll.qlRateHelperQuote(B34)</f>
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -3139,14 +3160,14 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0.2</v>
+      <c r="B4" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3309,15 +3330,15 @@
       </c>
       <c r="B16" s="12">
         <f>_xll.qlRateHelperQuote(B15)</f>
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C16" s="12">
         <f>_xll.qlRateHelperQuote(C15)</f>
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="D16" s="12">
         <f>_xll.qlRateHelperQuote(D15)</f>
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3419,14 +3440,14 @@
       <c r="A24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="C24" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="D24" s="12">
-        <v>0.6</v>
+      <c r="B24" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="C24" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="D24" s="20">
+        <v>0.03</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3517,15 +3538,15 @@
       </c>
       <c r="B31" s="12">
         <f>_xll.qlRateHelperQuote(B30)</f>
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="C31" s="12">
         <f>_xll.qlRateHelperQuote(C30)</f>
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="D31" s="12">
         <f>_xll.qlRateHelperQuote(D30)</f>
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3627,14 +3648,14 @@
       <c r="A39" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="12">
-        <v>0.33</v>
-      </c>
-      <c r="C39" s="12">
-        <v>0.33</v>
-      </c>
-      <c r="D39" s="12">
-        <v>0.33</v>
+      <c r="B39" s="19">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="C39" s="19">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="D39" s="19">
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3739,15 +3760,15 @@
       </c>
       <c r="B47" s="12">
         <f>_xll.qlRateHelperQuote(B46)</f>
-        <v>0.33</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="C47" s="12">
         <f>_xll.qlRateHelperQuote(C46)</f>
-        <v>0.33</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D47" s="12">
         <f>_xll.qlRateHelperQuote(D46)</f>
-        <v>0.33</v>
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -4086,10 +4107,10 @@
         <v>116</v>
       </c>
       <c r="B4" s="10">
-        <v>0.4</v>
+        <v>95.5</v>
       </c>
       <c r="C4" s="10">
-        <v>0.4</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4184,7 +4205,16 @@
       </c>
       <c r="B13" s="12" t="str">
         <f>_xll.qlFuturesRateHelper(B4,B5,B6,B7,B8,B9,B10)</f>
-        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R13C2FuturesRateHelper,A</v>
+        <v xml:space="preserve">Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+</v>
       </c>
       <c r="C13" s="12" t="str">
         <f>_xll.qlFuturesRateHelper(C4,C5,C6,C7,C8,C9,C10,,C12)</f>
@@ -4195,22 +4225,40 @@
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="12" t="str">
         <f>_xll.qlRateHelperQuote(B13)</f>
-        <v>0.4</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C14" s="12">
         <f>_xll.qlRateHelperQuote(C13)</f>
-        <v>0.4</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="11" t="str">
         <f>_xll.qlRateHelperLatestDate(B13)</f>
-        <v>45918</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C15" s="11">
         <f>_xll.qlRateHelperLatestDate(C13)</f>
@@ -4221,9 +4269,18 @@
       <c r="A16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="11" t="str">
         <f>_xll.qlRateHelperEarliestDate(B13)</f>
-        <v>45826</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C16" s="11">
         <f>_xll.qlRateHelperEarliestDate(C13)</f>
@@ -4234,9 +4291,18 @@
       <c r="A17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="11" t="str">
         <f>_xll.qlRateHelperMaturityDate(B13)</f>
-        <v>45918</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C17" s="11">
         <f>_xll.qlRateHelperMaturityDate(C13)</f>
@@ -4247,9 +4313,18 @@
       <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="11" t="str">
         <f>_xll.qlRateHelperLatestRelevantDate(B13)</f>
-        <v>45918</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C18" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(C13)</f>
@@ -4260,9 +4335,18 @@
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="11" t="str">
         <f>_xll.qlRateHelperPillarDate(B13)</f>
-        <v>45918</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C19" s="11">
         <f>_xll.qlRateHelperPillarDate(C13)</f>
@@ -4273,9 +4357,18 @@
       <c r="A20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="12" t="str">
         <f>_xll.qlFuturesRateConvexityAdjustment(B13)</f>
-        <v>0</v>
+        <v>Error in arg 1 'futures_rate_helper': Cannot convert 'Error in arg 9 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C20" s="12">
         <f>_xll.qlFuturesRateConvexityAdjustment(C13)</f>
@@ -4292,11 +4385,11 @@
       <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0.3</v>
+      <c r="B23" s="10">
+        <v>95.5</v>
+      </c>
+      <c r="C23" s="10">
+        <v>95.5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4356,7 +4449,16 @@
       </c>
       <c r="B29" t="str">
         <f>_xll.qlFuturesRateHelper2(B23,B24,B25,B26)</f>
-        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R29C2FuturesRateHelper,A</v>
+        <v xml:space="preserve">Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+</v>
       </c>
       <c r="C29" t="str">
         <f>_xll.qlFuturesRateHelper2(C23,C24,C25,C26,,C28)</f>
@@ -4367,22 +4469,40 @@
       <c r="A30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="12" t="str">
         <f>_xll.qlRateHelperQuote(B29)</f>
-        <v>0.3</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C30" s="12">
         <f>_xll.qlRateHelperQuote(C29)</f>
-        <v>0.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="11" t="str">
         <f>_xll.qlRateHelperLatestDate(B29)</f>
-        <v>45917</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C31" s="11">
         <f>_xll.qlRateHelperLatestDate(C29)</f>
@@ -4393,9 +4513,18 @@
       <c r="A32" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="11" t="str">
         <f>_xll.qlRateHelperEarliestDate(B29)</f>
-        <v>45826</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C32" s="11">
         <f>_xll.qlRateHelperEarliestDate(C29)</f>
@@ -4406,9 +4535,18 @@
       <c r="A33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="11" t="str">
         <f>_xll.qlRateHelperMaturityDate(B29)</f>
-        <v>45917</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C33" s="11">
         <f>_xll.qlRateHelperMaturityDate(C29)</f>
@@ -4419,9 +4557,18 @@
       <c r="A34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="11" t="str">
         <f>_xll.qlRateHelperLatestRelevantDate(B29)</f>
-        <v>45917</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C34" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(C29)</f>
@@ -4432,9 +4579,18 @@
       <c r="A35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="11" t="str">
         <f>_xll.qlRateHelperPillarDate(B29)</f>
-        <v>45917</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C35" s="11">
         <f>_xll.qlRateHelperPillarDate(C29)</f>
@@ -4445,9 +4601,18 @@
       <c r="A36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="12" t="str">
         <f>_xll.qlFuturesRateConvexityAdjustment(B29)</f>
-        <v>0</v>
+        <v>Error in arg 1 'futures_rate_helper': Cannot convert 'Error in arg 6 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C36" s="12">
         <f>_xll.qlFuturesRateConvexityAdjustment(C29)</f>
@@ -4458,11 +4623,11 @@
       <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="12">
-        <v>0.33</v>
-      </c>
-      <c r="C39" s="12">
-        <v>0.33</v>
+      <c r="B39" s="10">
+        <v>95.5</v>
+      </c>
+      <c r="C39" s="10">
+        <v>95.5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -4513,7 +4678,16 @@
       </c>
       <c r="B44" t="str">
         <f>_xll.qlFuturesRateHelper3(B39,B40,B41)</f>
-        <v>欣[test_ratehelpers.xlsx]FutureRateHelper!R44C2FuturesRateHelper,A</v>
+        <v xml:space="preserve">Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+</v>
       </c>
       <c r="C44" t="str">
         <f>_xll.qlFuturesRateHelper3(C39,C40,C41,,C43)</f>
@@ -4524,22 +4698,40 @@
       <c r="A45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="12" t="str">
         <f>_xll.qlRateHelperQuote(B44)</f>
-        <v>0.33</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C45" s="12">
         <f>_xll.qlRateHelperQuote(C44)</f>
-        <v>0.33</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="11" t="str">
         <f>_xll.qlRateHelperLatestDate(B44)</f>
-        <v>46009</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C46" s="11">
         <f>_xll.qlRateHelperLatestDate(C44)</f>
@@ -4550,9 +4742,18 @@
       <c r="A47" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="11" t="str">
         <f>_xll.qlRateHelperEarliestDate(B44)</f>
-        <v>45826</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C47" s="11">
         <f>_xll.qlRateHelperEarliestDate(C44)</f>
@@ -4563,9 +4764,18 @@
       <c r="A48" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="11" t="str">
         <f>_xll.qlRateHelperMaturityDate(B44)</f>
-        <v>46009</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C48" s="11">
         <f>_xll.qlRateHelperMaturityDate(C44)</f>
@@ -4576,9 +4786,18 @@
       <c r="A49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="11" t="str">
         <f>_xll.qlRateHelperLatestRelevantDate(B44)</f>
-        <v>46009</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C49" s="11">
         <f>_xll.qlRateHelperLatestRelevantDate(C44)</f>
@@ -4589,9 +4808,18 @@
       <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="11" t="str">
         <f>_xll.qlRateHelperPillarDate(B44)</f>
-        <v>46009</v>
+        <v>Error in arg 1 'rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C50" s="11">
         <f>_xll.qlRateHelperPillarDate(C44)</f>
@@ -4602,9 +4830,18 @@
       <c r="A51" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="12" t="str">
         <f>_xll.qlFuturesRateConvexityAdjustment(B44)</f>
-        <v>0</v>
+        <v>Error in arg 1 'futures_rate_helper': Cannot convert 'Error in arg 5 'type': ValueError: ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+Traceback (most recent call last):
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 36, in qFuturesType
+    return _qFuturesType(s)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\ratehelpers.py", line 32, in _qFuturesType
+    return enum_value(s, QL_FUTURES_TYPE)
+  File "C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\src\quantlib_xloil\utilities.py", line 22, in enum_value
+    raise ValueError(f"Cannot convert {string} using {str(enum_dict)}.")
+ValueError: Cannot convert &lt;class 'QuantLib.QuantLib.IMM'&gt; using {'IMM': 0, 'ASX': 1, 'CUSTOM': 2}.
+': Expected cache string</v>
       </c>
       <c r="C51" s="12">
         <f>_xll.qlFuturesRateConvexityAdjustment(C44)</f>
@@ -4654,14 +4891,14 @@
       <c r="A4" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0.4</v>
+      <c r="B4" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.04</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -4903,15 +5140,15 @@
       </c>
       <c r="B20" s="12">
         <f>_xll.qlRateHelperQuote(B19)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C20" s="12">
         <f>_xll.qlRateHelperQuote(C19)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="D20" s="12">
         <f>_xll.qlRateHelperQuote(D19)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5192,14 +5429,14 @@
       <c r="A40" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="C40" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="D40" s="12">
-        <v>0.4</v>
+      <c r="B40" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="C40" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="D40" s="18">
+        <v>0.04</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5318,15 +5555,15 @@
       </c>
       <c r="B50" s="12">
         <f>_xll.qlRateHelperQuote(B49)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="C50" s="12">
         <f>_xll.qlRateHelperQuote(C49)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="D50" s="12">
         <f>_xll.qlRateHelperQuote(D49)</f>
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -5574,14 +5811,14 @@
       <c r="A6" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.6</v>
+      <c r="B6" s="19">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C6" s="19">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="D6" s="19">
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5878,15 +6115,15 @@
       </c>
       <c r="B30" s="12">
         <f>_xll.qlRateHelperQuote(B29)</f>
-        <v>0.6</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="C30" s="12">
         <f>_xll.qlRateHelperQuote(C29)</f>
-        <v>0.6</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="D30" s="12">
         <f>_xll.qlRateHelperQuote(D29)</f>
-        <v>0.6</v>
+        <v>3.2000000000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -6032,10 +6269,10 @@
         <v>66</v>
       </c>
       <c r="B4" s="10">
-        <v>0.3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C4" s="10">
-        <v>0.3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -6043,10 +6280,10 @@
         <v>67</v>
       </c>
       <c r="B5" s="10">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="C5" s="10">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -6159,11 +6396,11 @@
       </c>
       <c r="B15" s="12">
         <f>_xll.qlRateHelperQuote(B14)</f>
-        <v>0.3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C15" s="12">
         <f>_xll.qlRateHelperQuote(C14)</f>
-        <v>0.3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -6237,11 +6474,11 @@
       </c>
       <c r="B21" s="12">
         <f>_xll.qlFxSwapRateHelperSpot(B14)</f>
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="C21" s="12">
         <f>_xll.qlFxSwapRateHelperSpot(C14)</f>
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
